--- a/media/Levels/kakeraMapLevel9.xlsx
+++ b/media/Levels/kakeraMapLevel9.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D723DD-1BD4-460E-A5A4-DCC28BC0C2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16CF90A-2309-4BC2-BF6E-D54B7372F0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="2508" yWindow="0" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Level_9" sheetId="1" r:id="rId1"/>
@@ -39358,28 +39358,28 @@
         <v>0</v>
       </c>
       <c r="BT86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB86">
         <v>0</v>
@@ -39813,28 +39813,28 @@
         <v>0</v>
       </c>
       <c r="BT87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB87">
         <v>0</v>
@@ -40268,28 +40268,28 @@
         <v>0</v>
       </c>
       <c r="BT88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB88">
         <v>0</v>
@@ -40723,28 +40723,28 @@
         <v>0</v>
       </c>
       <c r="BT89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB89">
         <v>0</v>
@@ -41178,28 +41178,28 @@
         <v>0</v>
       </c>
       <c r="BT90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB90">
         <v>0</v>
@@ -41633,28 +41633,28 @@
         <v>0</v>
       </c>
       <c r="BT91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB91">
         <v>0</v>
@@ -42088,28 +42088,28 @@
         <v>0</v>
       </c>
       <c r="BT92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB92">
         <v>0</v>
@@ -42543,28 +42543,28 @@
         <v>0</v>
       </c>
       <c r="BT93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB93">
         <v>0</v>
@@ -42998,28 +42998,28 @@
         <v>0</v>
       </c>
       <c r="BT94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB94">
         <v>0</v>
